--- a/港岛-寿臣山-寿臣山15号/寿臣山15号_销控明细表.xlsx
+++ b/港岛-寿臣山-寿臣山15号/寿臣山15号_销控明细表.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -947,7 +947,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1874,7 +1874,7 @@
         <is>
           <t>2号屋
 12073呎 (4+房)
-(24年-10月-31日)
+(24年-11月-01日)
 $8.45亿
 $69,991/呎</t>
         </is>
@@ -1883,7 +1883,7 @@
         <is>
           <t>3号屋
 9694呎 (4+房)
-(24年-08月-11日)
+(24年-08月-12日)
 $7.17亿
 $74,000/呎</t>
         </is>
@@ -1892,7 +1892,7 @@
         <is>
           <t>5号屋
 6695呎 (4+房)
-(24年-03月-04日)
+(24年-03月-05日)
 $4.98亿
 $74,400/呎</t>
         </is>
@@ -1901,7 +1901,7 @@
         <is>
           <t>6号屋
 9550呎 (4+房)
-(25年-10月-15日)
+(25年-10月-16日)
 $5.79亿
 $60,623/呎</t>
         </is>
@@ -1910,7 +1910,7 @@
         <is>
           <t>7号屋
 8032呎 (4+房)
-(22年-07月-21日)
+(22年-07月-22日)
 $8.70亿
 $108,347/呎</t>
         </is>
@@ -1926,7 +1926,7 @@
         <is>
           <t>8号屋
 2746呎 (4+房)
-(24年-05月-21日)
+(24年-05月-22日)
 $2.60亿
 $94,670/呎</t>
         </is>
@@ -1935,7 +1935,7 @@
         <is>
           <t>9号屋
 3727呎 (4+房)
-(26年-01月-26日)
+(26年-01月-27日)
 $2.25亿
 $60,263/呎</t>
         </is>
@@ -1944,7 +1944,7 @@
         <is>
           <t>10号屋
 4853呎 (4+房)
-(26年-01月-26日)
+(26年-01月-27日)
 $2.92亿
 $60,264/呎</t>
         </is>
@@ -1953,7 +1953,7 @@
         <is>
           <t>11号屋
 4759呎 (4+房)
-(22年-08月-07日)
+(22年-08月-08日)
 $4.35亿
 $91,406/呎</t>
         </is>
@@ -1962,7 +1962,7 @@
         <is>
           <t>12号屋
 4696呎 (4+房)
-(24年-07月-29日)
+(24年-07月-30日)
 $3.20亿
 $68,177/呎</t>
         </is>
@@ -1971,7 +1971,7 @@
         <is>
           <t>15号屋
 4696呎 (4+房)
-(26年-01月-06日)
+(26年-01月-07日)
 $2.90亿
 $61,725/呎</t>
         </is>

--- a/港岛-寿臣山-寿臣山15号/寿臣山15号_销控明细表.xlsx
+++ b/港岛-寿臣山-寿臣山15号/寿臣山15号_销控明细表.xlsx
@@ -116,7 +116,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -159,12 +159,6 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -192,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -246,9 +240,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -616,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -919,7 +910,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>5号屋</t>
+          <t>6号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -938,7 +929,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6695</v>
+        <v>9550</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -947,14 +938,14 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>498108000</v>
+        <v>578950000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>74400</v>
+        <v>60623</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -985,7 +976,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6号屋</t>
+          <t>9号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1004,7 +995,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9550</v>
+        <v>3727</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1013,14 +1004,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>578950000</v>
+        <v>224600200</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>60623</v>
+        <v>60263</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1051,7 +1042,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>7号屋</t>
+          <t>10号屋</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1070,7 +1061,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8032</v>
+        <v>4853</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1079,14 +1070,14 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>870240000</v>
+        <v>292459700</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>108347</v>
+        <v>60264</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1108,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>8号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1136,7 +1127,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2746</v>
+        <v>4759</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1145,14 +1136,14 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2022-08-08</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>259964000</v>
+        <v>435000000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>94670</v>
+        <v>91406</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1183,7 +1174,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>9号屋</t>
+          <t>12号屋</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1202,7 +1193,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>3727</v>
+        <v>4696</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1211,14 +1202,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>224600200</v>
+        <v>320160000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>60263</v>
+        <v>68177</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1249,7 +1240,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>15号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1268,7 +1259,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4853</v>
+        <v>4696</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1277,14 +1268,14 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>292459700</v>
+        <v>289860000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>60264</v>
+        <v>61725</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1315,7 +1306,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>16号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1334,23 +1325,27 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4759</v>
+        <v>4025</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>435000000</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>91406</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1359,12 +1354,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1374,14 +1369,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>17号屋</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1400,23 +1395,27 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>4696</v>
+        <v>3777</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>320160000</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>68177</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1425,12 +1424,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1440,14 +1439,14 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>15号屋</t>
+          <t>18号屋</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1466,23 +1465,27 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4696</v>
+        <v>4906</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>289860000</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>61725</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1505,216 +1508,6 @@
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>16号屋</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>4025</v>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>17号屋</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>3777</v>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>18号屋</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>4906</v>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1735,7 +1528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1789,7 +1582,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>15 套</t>
+          <t>12 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1804,7 +1597,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>11 套</t>
+          <t>8 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1890,15 +1683,6 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>5号屋
-6695呎 (4+房)
-(24年-03月-05日)
-$4.98亿
-$74,400/呎</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
           <t>6号屋
 9550呎 (4+房)
 (25年-10月-16日)
@@ -1906,32 +1690,7 @@
 $60,623/呎</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>7号屋
-8032呎 (4+房)
-(22年-07月-22日)
-$8.70亿
-$108,347/呎</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>第 2 行</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>8号屋
-2746呎 (4+房)
-(24年-05月-22日)
-$2.60亿
-$94,670/呎</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>9号屋
 3727呎 (4+房)
@@ -1940,7 +1699,7 @@
 $60,263/呎</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>10号屋
 4853呎 (4+房)
@@ -1949,7 +1708,14 @@
 $60,264/呎</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>11号屋
 4759呎 (4+房)
@@ -1958,7 +1724,7 @@
 $91,406/呎</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>12号屋
 4696呎 (4+房)
@@ -1967,7 +1733,7 @@
 $68,177/呎</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>15号屋
 4696呎 (4+房)
@@ -1976,14 +1742,7 @@
 $61,725/呎</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>第 3 行</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>16号屋
 4025呎 (4+房)
@@ -1992,7 +1751,7 @@
 -</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>17号屋
 3777呎 (4+房)
@@ -2001,7 +1760,7 @@
 -</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>18号屋
 4906呎 (4+房)
@@ -2010,9 +1769,6 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr"/>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/港岛-寿臣山-寿臣山15号/寿臣山15号_销控明细表.xlsx
+++ b/港岛-寿臣山-寿臣山15号/寿臣山15号_销控明细表.xlsx
@@ -116,7 +116,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -159,6 +159,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -186,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -240,6 +246,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -607,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -910,7 +919,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6号屋</t>
+          <t>5号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -929,7 +938,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9550</v>
+        <v>6695</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -938,14 +947,14 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2024-03-05</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>578950000</v>
+        <v>498108000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>60623</v>
+        <v>74400</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -976,7 +985,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>9号屋</t>
+          <t>6号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -995,7 +1004,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3727</v>
+        <v>9550</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1004,14 +1013,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>224600200</v>
+        <v>578950000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>60263</v>
+        <v>60623</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1042,7 +1051,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>7号屋</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1061,7 +1070,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4853</v>
+        <v>8032</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1070,14 +1079,14 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>292459700</v>
+        <v>870240000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>60264</v>
+        <v>108347</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1108,7 +1117,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>8号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1127,7 +1136,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4759</v>
+        <v>2746</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1136,14 +1145,14 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2022-08-08</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>435000000</v>
+        <v>259964000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>91406</v>
+        <v>94670</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1174,7 +1183,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>9号屋</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1193,7 +1202,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4696</v>
+        <v>3727</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1202,14 +1211,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2024-07-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>320160000</v>
+        <v>224600200</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>68177</v>
+        <v>60263</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1240,7 +1249,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>15号屋</t>
+          <t>10号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1259,7 +1268,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4696</v>
+        <v>4853</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1268,14 +1277,14 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>289860000</v>
+        <v>292459700</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>61725</v>
+        <v>60264</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1306,7 +1315,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>16号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1325,27 +1334,23 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4025</v>
+        <v>4759</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>435000000</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>91406</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1354,12 +1359,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1369,14 +1374,14 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>17号屋</t>
+          <t>12号屋</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1395,27 +1400,23 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3777</v>
+        <v>4696</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2024-07-30</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>320160000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>68177</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1424,12 +1425,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1439,75 +1440,281 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>15号屋</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>4696</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>289860000</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>61725</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>16号屋</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>4025</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>17号屋</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>3777</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>在售</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>18号屋</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E17" s="4" t="n">
         <v>4906</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1528,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1582,7 +1789,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>12 套</t>
+          <t>15 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1597,7 +1804,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>8 套</t>
+          <t>11 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1683,6 +1890,15 @@
       </c>
       <c r="E6" s="17" t="inlineStr">
         <is>
+          <t>5号屋
+6695呎 (4+房)
+(24年-03月-05日)
+$4.98亿
+$74,400/呎</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
           <t>6号屋
 9550呎 (4+房)
 (25年-10月-16日)
@@ -1690,7 +1906,32 @@
 $60,623/呎</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>7号屋
+8032呎 (4+房)
+(22年-07月-22日)
+$8.70亿
+$108,347/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>8号屋
+2746呎 (4+房)
+(24年-05月-22日)
+$2.60亿
+$94,670/呎</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>9号屋
 3727呎 (4+房)
@@ -1699,7 +1940,7 @@
 $60,263/呎</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>10号屋
 4853呎 (4+房)
@@ -1708,14 +1949,7 @@
 $60,264/呎</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>第 2 行</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>11号屋
 4759呎 (4+房)
@@ -1724,7 +1958,7 @@
 $91,406/呎</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>12号屋
 4696呎 (4+房)
@@ -1733,7 +1967,7 @@
 $68,177/呎</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>15号屋
 4696呎 (4+房)
@@ -1742,7 +1976,14 @@
 $61,725/呎</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>第 3 行</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>16号屋
 4025呎 (4+房)
@@ -1751,7 +1992,7 @@
 -</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>17号屋
 3777呎 (4+房)
@@ -1760,7 +2001,7 @@
 -</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>18号屋
 4906呎 (4+房)
@@ -1769,6 +2010,9 @@
 暂无呎价</t>
         </is>
       </c>
+      <c r="E8" s="19" t="inlineStr"/>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
